--- a/data/chatflow_test_data.xlsx
+++ b/data/chatflow_test_data.xlsx
@@ -1,60 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>expect</t>
-  </si>
-  <si>
-    <t>predict</t>
-  </si>
-  <si>
-    <t>node_traces</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -385,38 +420,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>expect</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gold_node_traces</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>买三包化肥</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>11111</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>2</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>我要查一下上个月的订单</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>22222</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/chatflow_test_data.xlsx
+++ b/data/chatflow_test_data.xlsx
@@ -1,43 +1,1714 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28260" windowHeight="14020"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>expect</t>
+  </si>
+  <si>
+    <t>gold_node_traces</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>买三包化肥</t>
+  </si>
+  <si>
+    <t>我找到这些商品，您可以回复‘第几个商品’继续查看：
+1. 赤天化尿素（95元/袋，库存212）
+2. 西洋复合肥（15:15:15）（142.5元/袋，库存195）
+3. 赤天化复合肥（15:15:15）（142.5元/袋，库存200）
+4. 长效追一道（尿素）24:0:5（76元/袋，库存200）
+5. 谷润之藻生根（100元/kg，库存0）
+6. 谷润之矿源腐植酸钾20-20-20（130元/kg，库存0）
+7. 含腐植酸水溶肥（180元/kg，库存0）
+8. 百倍邦土壤调理剂（40元/kg，库存0）
+9. 生物有机肥0.2亿（颗粒）（70元/kg，库存0）
+10. 生物有机肥0.2亿（粉状）（60元/kg，库存0）</t>
+  </si>
+  <si>
+    <t>[用户输入]:
+{
+  "customer_id": "11111",
+  "sys.files": [],
+  "sys.user_id": "abc-123",
+  "sys.app_id": "735c9c90-b795-4287-b018-cc72f6a9106a",
+  "sys.workflow_id": "5675993e-1c2c-4071-98c1-699ff12b4516",
+  "sys.workflow_run_id": "7484edf6-b8d7-46ed-99c5-fa06bea0b9d9",
+  "sys.query": "买三包化肥",
+  "sys.conversation_id": "622355c8-18c0-47b8-8382-f50189e96b5f",
+  "sys.dialogue_count": 1
+}
+[路由判断]:
+{
+  "text": {
+    "intent": "SHOPPING",
+    "confidence": 99,
+    "switch_from": "",
+    "switch_to": "",
+    "clarify_question": ""
+  },
+  "reasoning_content": "",
+  "usage": {
+    "prompt_tokens": 399,
+    "prompt_unit_price": "0.86",
+    "prompt_price_unit": "0.000001",
+    "prompt_price": "0.0003431",
+    "completion_tokens": 29,
+    "completion_unit_price": "1.29",
+    "completion_price_unit": "0.000001",
+    "completion_price": "0.0000374",
+    "total_tokens": 428,
+    "total_price": "0.0003805",
+    "currency": "RMB",
+    "latency": 4.882,
+    "time_to_first_token": 3.068,
+    "time_to_generate": 1.814
+  },
+  "finish_reason": "stop"
+}
+[解析置信度JSON]:
+{
+  "clarify_question": "",
+  "clear_recommend": "clear",
+  "confidence": 99,
+  "confidence_level": "HIGH",
+  "intent_router": "SHOPPING",
+  "recommend_goods_id": "",
+  "recommend_goods_name": "",
+  "switch_from": "",
+  "switch_to": "",
+  "route_mode": "NORMAL"
+}
+[置信度≥95%？]:
+{
+  "result": true,
+  "selected_case_id": "true"
+}
+[切换预处理]:
+{
+  "dispatch_intent": "SHOPPING",
+  "dispatch_query": "买三包化肥",
+  "shop_status": "IDLE",
+  "action": "",
+  "order_context": {},
+  "category_cache": [],
+  "candidate_cache": [],
+  "address_cache": [],
+  "last_goods_detail": {},
+  "current_flow_id": "",
+  "goods_order_cache": [],
+  "plot_status": "STAGE_SEARCH",
+  "contractor_cache": [],
+  "plot_cache": [],
+  "selected_contractor_code": "",
+  "selected_plot_id": "",
+  "selected_plot_name": "",
+  "fs_status": "STAGE_FS_SEARCH",
+  "fs_selected_service_id": "",
+  "fs_selected_service_name": "",
+  "fs_selected_unit_price": "",
+  "fs_selected_price_unit": "",
+  "fs_selected_plot_codes": "",
+  "fs_selected_plot_names": "",
+  "fs_selected_total_area": "",
+  "fs_expect_time": "",
+  "fs_remark": "",
+  "fs_candidate_cache": "",
+  "fs_plot_candidate_cache": "",
+  "fs_order_cache": "",
+  "pending_plot_indices": "",
+  "pending_time_text": "",
+  "in_recommend_flow": "false",
+  "recommend_candidate_cache": []
+}
+[写回切换状态]:
+{}
+[条件分支]:
+{
+  "result": true,
+  "selected_case_id": "true"
+}
+[下单LLM]:
+{
+  "text": {
+    "action": "search_goods",
+    "query": "化肥"
+  },
+  "reasoning_content": "",
+  "usage": {
+    "prompt_tokens": 1033,
+    "prompt_unit_price": "0.86",
+    "prompt_price_unit": "0.000001",
+    "prompt_price": "0.0008884",
+    "completion_tokens": 12,
+    "completion_unit_price": "1.29",
+    "completion_price_unit": "0.000001",
+    "completion_price": "0.0000155",
+    "total_tokens": 1045,
+    "total_price": "0.0009039",
+    "currency": "RMB",
+    "latency": 4.21,
+    "time_to_first_token": 2.914,
+    "time_to_generate": 1.296
+  },
+  "finish_reason": "stop"
+}
+[变量提取]:
+{
+  "action": "search_goods",
+  "address_id": "",
+  "category_id": "",
+  "goods_id": "",
+  "order_id": "",
+  "quantity": "",
+  "query": "化肥",
+  "sku_id": ""
+}
+[下单工具-v0.0.3-含订单查询]:
+{
+  "text": {
+    "reply_text": {
+      "action": "search_goods",
+      "reply_text": "我找到这些商品，您可以回复‘第几个商品’继续查看：\n1. 赤天化尿素（95元/袋，库存212）\n2. 西洋复合肥（15:15:15）（142.5元/袋，库存195）\n3. 赤天化复合肥（15:15:15）（142.5元/袋，库存200）\n4. 长效追一道（尿素）24:0:5（76元/袋，库存200）\n5. 谷润之藻生根（100元/kg，库存0）\n6. 谷润之矿源腐植酸钾20-20-20（130元/kg，库存0）\n7. 含腐植酸水溶肥（180元/kg，库存0）\n8. 百倍邦土壤调理剂（40元/kg，库存0）\n9. 生物有机肥0.2亿（颗粒）（70元/kg，库存0）\n10. 生物有机肥0.2亿（粉状）（60元/kg，库存0）",
+      "shop_status": "WAITING_SELECT_GOODS",
+      "order_context": {
+        "goods_id": "",
+        "goods_name": "",
+        "sku_id": "",
+        "sku_name": "",
+        "quantity": "",
+        "address_id": "",
+        "address_text": ""
+      },
+      "category_cache": [],
+      "candidate_cache": [
+        {
+          "index": 1,
+          "id": "2019755410711867393",
+          "goods_id": "2019755410711867393",
+          "name": "赤天化尿素",
+          "unit": "袋",
+          "price": "95",
+          "price_desc": "95元/袋",
+          "stock": 212,
+          "brand_name": "赤牌",
+          "spec_type": "single"
+        },
+        {
+          "index": 2,
+          "id": "2019755634339573762",
+          "goods_id": "2019755634339573762",
+          "name": "西洋复合肥（15:15:15）",
+          "unit": "袋",
+          "price": "142.5",
+          "price_desc": "142.5元/袋",
+          "stock": 195,
+          "brand_name": "西洋",
+          "spec_type": "single"
+        },
+        {
+          "index": 3,
+          "id": "2019756488069181442",
+          "goods_id": "2019756488069181442",
+          "name": "赤天化复合肥（15:15:15）",
+          "unit": "袋",
+          "price": "142.5",
+          "price_desc": "142.5元/袋",
+          "stock": 200,
+          "brand_name": "赤天化",
+          "spec_type": "single"
+        },
+        {
+          "index": 4,
+          "id": "2019756165824999425",
+          "goods_id": "2019756165824999425",
+          "name": "长效追一道（尿素）24:0:5",
+          "unit": "袋",
+          "price": "76",
+          "price_desc": "76元/袋",
+          "stock": 200,
+          "brand_name": "佰禾肥业",
+          "spec_type": "single"
+        },
+        {
+          "index": 5,
+          "id": "2039268890938216449",
+          "goods_id": "2039268890938216449",
+          "name": "谷润之藻生根",
+          "unit": "kg",
+          "price": "100",
+          "price_desc": "100元/kg",
+          "stock": 0,
+          "brand_name": "谷之润",
+          "spec_type": "single"
+        },
+        {
+          "index": 6,
+          "id": "2039268560259289090",
+          "goods_id": "2039268560259289090",
+          "name": "谷润之矿源腐植酸钾20-20-20",
+          "unit": "kg",
+          "price": "130",
+          "price_desc": "130元/kg",
+          "stock": 0,
+          "brand_name": "谷之润",
+          "spec_type": "single"
+        },
+        {
+          "index": 7,
+          "id": "2039268015851212802",
+          "goods_id": "2039268015851212802",
+          "name": "含腐植酸水溶肥",
+          "unit": "kg",
+          "price": "180",
+          "price_desc": "180元/kg",
+          "stock": 0,
+          "brand_name": "奥姆斯特",
+          "spec_type": "single"
+        },
+        {
+          "index": 8,
+          "id": "2039267600099217410",
+          "goods_id": "2039267600099217410",
+          "name": "百倍邦土壤调理剂",
+          "unit": "kg",
+          "price": "40",
+          "price_desc": "40元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 9,
+          "id": "2039267323740721154",
+          "goods_id": "2039267323740721154",
+          "name": "生物有机肥0.2亿（颗粒）",
+          "unit": "kg",
+          "price": "70",
+          "price_desc": "70元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 10,
+          "id": "2039266981347102721",
+          "goods_id": "2039266981347102721",
+          "name": "生物有机肥0.2亿（粉状）",
+          "unit": "kg",
+          "price": "60",
+          "price_desc": "60元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 11,
+          "id": "2039265582534135810",
+          "goods_id": "2039265582534135810",
+          "name": "洋丰豆生物有机肥",
+          "unit": "kg",
+          "price": "90",
+          "price_desc": "90元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 12,
+          "id": "2039265334109704193",
+          "goods_id": "2039265334109704193",
+          "name": "洋丰复合肥（追一道）玉米专用",
+          "unit": "kg",
+          "price": "125",
+          "price_desc": "125元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 13,
+          "id": "2039263960278011905",
+          "goods_id": "2039263960278011905",
+          "name": "洋丰锌磷镁复合肥25-10-16",
+          "unit": "kg",
+          "price": "180",
+          "price_desc": "180元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 14,
+          "id": "2039263622888198145",
+          "goods_id": "2039263622888198145",
+          "name": "洋丰锌磷镁复合肥17-17-17",
+          "unit": "kg",
+          "price": "220",
+          "price_desc": "220元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 15,
+          "id": "2039263225414979586",
+          "goods_id": "2039263225414979586",
+          "name": "洋丰复合肥14-16-15",
+          "unit": "kg",
+          "price": "160",
+          "price_desc": "160元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 16,
+          "id": "2039262979989475329",
+          "goods_id": "2039262979989475329",
+          "name": "洋丰复合肥15-15-15",
+          "unit": "kg",
+          "price": "160",
+          "price_desc": "160元/kg",
+          "stock": 0,
+          "brand_name": "新洋丰",
+          "spec_type": "single"
+        },
+        {
+          "index": 17,
+          "id": "2019743727796842497",
+          "goods_id": "2019743727796842497",
+          "name": "菌安天下",
+          "unit": "瓶",
+          "price": "19",
+          "price_desc": "19元/瓶",
+          "stock": 200,
+          "brand_name": "安利绿色",
+          "spec_type": "single"
+        }
+      ],
+      "address_cache": [],
+      "last_goods_detail": {},
+      "current_flow_id": ""
+    }
+  },
+  "files": [],
+  "json": [
+    {
+      "reply_text": {
+        "action": "search_goods",
+        "reply_text": "我找到这些商品，您可以回复‘第几个商品’继续查看：\n1. 赤天化尿素（95元/袋，库存212）\n2. 西洋复合肥（15:15:15）（142.5元/袋，库存195）\n3. 赤天化复合肥（15:15:15）（142.5元/袋，库存200）\n4. 长效追一道（尿素）24:0:5（76元/袋，库存200）\n5. 谷润之藻生根（100元/kg，库存0）\n6. 谷润之矿源腐植酸钾20-20-20（130元/kg，库存0）\n7. 含腐植酸水溶肥（180元/kg，库存0）\n8. 百倍邦土壤调理剂（40元/kg，库存0）\n9. 生物有机肥0.2亿（颗粒）（70元/kg，库存0）\n10. 生物有机肥0.2亿（粉状）（60元/kg，库存0）",
+        "shop_status": "WAITING_SELECT_GOODS",
+        "order_context": {
+          "goods_id": "",
+          "goods_name": "",
+          "sku_id": "",
+          "sku_name": "",
+          "quantity": "",
+          "address_id": "",
+          "address_text": ""
+        },
+        "category_cache": [],
+        "candidate_cache": [
+          {
+            "index": 1,
+            "id": "2019755410711867393",
+            "goods_id": "2019755410711867393",
+            "name": "赤天化尿素",
+            "unit": "袋",
+            "price": "95",
+            "price_desc": "95元/袋",
+            "stock": 212,
+            "brand_name": "赤牌",
+            "spec_type": "single"
+          },
+          {
+            "index": 2,
+            "id": "2019755634339573762",
+            "goods_id": "2019755634339573762",
+            "name": "西洋复合肥（15:15:15）",
+            "unit": "袋",
+            "price": "142.5",
+            "price_desc": "142.5元/袋",
+            "stock": 195,
+            "brand_name": "西洋",
+            "spec_type": "single"
+          },
+          {
+            "index": 3,
+            "id": "2019756488069181442",
+            "goods_id": "2019756488069181442",
+            "name": "赤天化复合肥（15:15:15）",
+            "unit": "袋",
+            "price": "142.5",
+            "price_desc": "142.5元/袋",
+            "stock": 200,
+            "brand_name": "赤天化",
+            "spec_type": "single"
+          },
+          {
+            "index": 4,
+            "id": "2019756165824999425",
+            "goods_id": "2019756165824999425",
+            "name": "长效追一道（尿素）24:0:5",
+            "unit": "袋",
+            "price": "76",
+            "price_desc": "76元/袋",
+            "stock": 200,
+            "brand_name": "佰禾肥业",
+            "spec_type": "single"
+          },
+          {
+            "index": 5,
+            "id": "2039268890938216449",
+            "goods_id": "2039268890938216449",
+            "name": "谷润之藻生根",
+            "unit": "kg",
+            "price": "100",
+            "price_desc": "100元/kg",
+            "stock": 0,
+            "brand_name": "谷之润",
+            "spec_type": "single"
+          },
+          {
+            "index": 6,
+            "id": "2039268560259289090",
+            "goods_id": "2039268560259289090",
+            "name": "谷润之矿源腐植酸钾20-20-20",
+            "unit": "kg",
+            "price": "130",
+            "price_desc": "130元/kg",
+            "stock": 0,
+            "brand_name": "谷之润",
+            "spec_type": "single"
+          },
+          {
+            "index": 7,
+            "id": "2039268015851212802",
+            "goods_id": "2039268015851212802",
+            "name": "含腐植酸水溶肥",
+            "unit": "kg",
+            "price": "180",
+            "price_desc": "180元/kg",
+            "stock": 0,
+            "brand_name": "奥姆斯特",
+            "spec_type": "single"
+          },
+          {
+            "index": 8,
+            "id": "2039267600099217410",
+            "goods_id": "2039267600099217410",
+            "name": "百倍邦土壤调理剂",
+            "unit": "kg",
+            "price": "40",
+            "price_desc": "40元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 9,
+            "id": "2039267323740721154",
+            "goods_id": "2039267323740721154",
+            "name": "生物有机肥0.2亿（颗粒）",
+            "unit": "kg",
+            "price": "70",
+            "price_desc": "70元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 10,
+            "id": "2039266981347102721",
+            "goods_id": "2039266981347102721",
+            "name": "生物有机肥0.2亿（粉状）",
+            "unit": "kg",
+            "price": "60",
+            "price_desc": "60元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 11,
+            "id": "2039265582534135810",
+            "goods_id": "2039265582534135810",
+            "name": "洋丰豆生物有机肥",
+            "unit": "kg",
+            "price": "90",
+            "price_desc": "90元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 12,
+            "id": "2039265334109704193",
+            "goods_id": "2039265334109704193",
+            "name": "洋丰复合肥（追一道）玉米专用",
+            "unit": "kg",
+            "price": "125",
+            "price_desc": "125元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 13,
+            "id": "2039263960278011905",
+            "goods_id": "2039263960278011905",
+            "name": "洋丰锌磷镁复合肥25-10-16",
+            "unit": "kg",
+            "price": "180",
+            "price_desc": "180元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 14,
+            "id": "2039263622888198145",
+            "goods_id": "2039263622888198145",
+            "name": "洋丰锌磷镁复合肥17-17-17",
+            "unit": "kg",
+            "price": "220",
+            "price_desc": "220元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 15,
+            "id": "2039263225414979586",
+            "goods_id": "2039263225414979586",
+            "name": "洋丰复合肥14-16-15",
+            "unit": "kg",
+            "price": "160",
+            "price_desc": "160元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 16,
+            "id": "2039262979989475329",
+            "goods_id": "2039262979989475329",
+            "name": "洋丰复合肥15-15-15",
+            "unit": "kg",
+            "price": "160",
+            "price_desc": "160元/kg",
+            "stock": 0,
+            "brand_name": "新洋丰",
+            "spec_type": "single"
+          },
+          {
+            "index": 17,
+            "id": "2019743727796842497",
+            "goods_id": "2019743727796842497",
+            "name": "菌安天下",
+            "unit": "瓶",
+            "price": "19",
+            "price_desc": "19元/瓶",
+            "stock": 200,
+            "brand_name": "安利绿色",
+            "spec_type": "single"
+          }
+        ],
+        "address_cache": [],
+        "last_goods_detail": {},
+        "current_flow_id": ""
+      }
+    }
+  ],
+  "reply_text": {
+    "action": "search_goods",
+    "reply_text": "我找到这些商品，您可以回复‘第几个商品’继续查看：\n1. 赤天化尿素（95元/袋，库存212）\n2. 西洋复合肥（15:15:15）（142.5元/袋，库存195）\n3. 赤天化复合肥（15:15:15）（142.5元/袋，库存200）\n4. 长效追一道（尿素）24:0:5（76元/袋，库存200）\n5. 谷润之藻生根（100元/kg，库存0）\n6. 谷润之矿源腐植酸钾20-20-20（130元/kg，库存0）\n7. 含腐植酸水溶肥（180元/kg，库存0）\n8. 百倍邦土壤调理剂（40元/kg，库存0）\n9. 生物有机肥0.2亿（颗粒）（70元/kg，库存0）\n10. 生物有机肥0.2亿（粉状）（60元/kg，库存0）",
+    "shop_status": "WAITING_SELECT_GOODS",
+    "order_context": {
+      "goods_id": "",
+      "goods_name": "",
+      "sku_id": "",
+      "sku_name": "",
+      "quantity": "",
+      "address_id": "",
+      "address_text": ""
+    },
+    "category_cache": [],
+    "candidate_cache": [
+      {
+        "index": 1,
+        "id": "2019755410711867393",
+        "goods_id": "2019755410711867393",
+        "name": "赤天化尿素",
+        "unit": "袋",
+        "price": "95",
+        "price_desc": "95元/袋",
+        "stock": 212,
+        "brand_name": "赤牌",
+        "spec_type": "single"
+      },
+      {
+        "index": 2,
+        "id": "2019755634339573762",
+        "goods_id": "2019755634339573762",
+        "name": "西洋复合肥（15:15:15）",
+        "unit": "袋",
+        "price": "142.5",
+        "price_desc": "142.5元/袋",
+        "stock": 195,
+        "brand_name": "西洋",
+        "spec_type": "single"
+      },
+      {
+        "index": 3,
+        "id": "2019756488069181442",
+        "goods_id": "2019756488069181442",
+        "name": "赤天化复合肥（15:15:15）",
+        "unit": "袋",
+        "price": "142.5",
+        "price_desc": "142.5元/袋",
+        "stock": 200,
+        "brand_name": "赤天化",
+        "spec_type": "single"
+      },
+      {
+        "index": 4,
+        "id": "2019756165824999425",
+        "goods_id": "2019756165824999425",
+        "name": "长效追一道（尿素）24:0:5",
+        "unit": "袋",
+        "price": "76",
+        "price_desc": "76元/袋",
+        "stock": 200,
+        "brand_name": "佰禾肥业",
+        "spec_type": "single"
+      },
+      {
+        "index": 5,
+        "id": "2039268890938216449",
+        "goods_id": "2039268890938216449",
+        "name": "谷润之藻生根",
+        "unit": "kg",
+        "price": "100",
+        "price_desc": "100元/kg",
+        "stock": 0,
+        "brand_name": "谷之润",
+        "spec_type": "single"
+      },
+      {
+        "index": 6,
+        "id": "2039268560259289090",
+        "goods_id": "2039268560259289090",
+        "name": "谷润之矿源腐植酸钾20-20-20",
+        "unit": "kg",
+        "price": "130",
+        "price_desc": "130元/kg",
+        "stock": 0,
+        "brand_name": "谷之润",
+        "spec_type": "single"
+      },
+      {
+        "index": 7,
+        "id": "2039268015851212802",
+        "goods_id": "2039268015851212802",
+        "name": "含腐植酸水溶肥",
+        "unit": "kg",
+        "price": "180",
+        "price_desc": "180元/kg",
+        "stock": 0,
+        "brand_name": "奥姆斯特",
+        "spec_type": "single"
+      },
+      {
+        "index": 8,
+        "id": "2039267600099217410",
+        "goods_id": "2039267600099217410",
+        "name": "百倍邦土壤调理剂",
+        "unit": "kg",
+        "price": "40",
+        "price_desc": "40元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 9,
+        "id": "2039267323740721154",
+        "goods_id": "2039267323740721154",
+        "name": "生物有机肥0.2亿（颗粒）",
+        "unit": "kg",
+        "price": "70",
+        "price_desc": "70元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 10,
+        "id": "2039266981347102721",
+        "goods_id": "2039266981347102721",
+        "name": "生物有机肥0.2亿（粉状）",
+        "unit": "kg",
+        "price": "60",
+        "price_desc": "60元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 11,
+        "id": "2039265582534135810",
+        "goods_id": "2039265582534135810",
+        "name": "洋丰豆生物有机肥",
+        "unit": "kg",
+        "price": "90",
+        "price_desc": "90元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 12,
+        "id": "2039265334109704193",
+        "goods_id": "2039265334109704193",
+        "name": "洋丰复合肥（追一道）玉米专用",
+        "unit": "kg",
+        "price": "125",
+        "price_desc": "125元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 13,
+        "id": "2039263960278011905",
+        "goods_id": "2039263960278011905",
+        "name": "洋丰锌磷镁复合肥25-10-16",
+        "unit": "kg",
+        "price": "180",
+        "price_desc": "180元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 14,
+        "id": "2039263622888198145",
+        "goods_id": "2039263622888198145",
+        "name": "洋丰锌磷镁复合肥17-17-17",
+        "unit": "kg",
+        "price": "220",
+        "price_desc": "220元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 15,
+        "id": "2039263225414979586",
+        "goods_id": "2039263225414979586",
+        "name": "洋丰复合肥14-16-15",
+        "unit": "kg",
+        "price": "160",
+        "price_desc": "160元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 16,
+        "id": "2039262979989475329",
+        "goods_id": "2039262979989475329",
+        "name": "洋丰复合肥15-15-15",
+        "unit": "kg",
+        "price": "160",
+        "price_desc": "160元/kg",
+        "stock": 0,
+        "brand_name": "新洋丰",
+        "spec_type": "single"
+      },
+      {
+        "index": 17,
+        "id": "2019743727796842497",
+        "goods_id": "2019743727796842497",
+        "name": "菌安天下",
+        "unit": "瓶",
+        "price": "19",
+        "price_desc": "19元/瓶",
+        "stock": 200,
+        "brand_name": "安利绿色",
+        "spec_type": "single"
+      }
+    ],
+    "address_cache": [],
+    "last_goods_detail": {},
+    "current_flow_id": ""
+  }
+}
+[代码执行 2]:
+{
+  "action": "search_goods",
+  "address_cache_json": [],
+  "candidate_cache_json": [
+    {
+      "index": 1,
+      "id": "2019755410711867393",
+      "goods_id": "2019755410711867393",
+      "name": "赤天化尿素",
+      "unit": "袋",
+      "price": "95",
+      "price_desc": "95元/袋",
+      "stock": 212,
+      "brand_name": "赤牌",
+      "spec_type": "single"
+    },
+    {
+      "index": 2,
+      "id": "2019755634339573762",
+      "goods_id": "2019755634339573762",
+      "name": "西洋复合肥（15:15:15）",
+      "unit": "袋",
+      "price": "142.5",
+      "price_desc": "142.5元/袋",
+      "stock": 195,
+      "brand_name": "西洋",
+      "spec_type": "single"
+    },
+    {
+      "index": 3,
+      "id": "2019756488069181442",
+      "goods_id": "2019756488069181442",
+      "name": "赤天化复合肥（15:15:15）",
+      "unit": "袋",
+      "price": "142.5",
+      "price_desc": "142.5元/袋",
+      "stock": 200,
+      "brand_name": "赤天化",
+      "spec_type": "single"
+    },
+    {
+      "index": 4,
+      "id": "2019756165824999425",
+      "goods_id": "2019756165824999425",
+      "name": "长效追一道（尿素）24:0:5",
+      "unit": "袋",
+      "price": "76",
+      "price_desc": "76元/袋",
+      "stock": 200,
+      "brand_name": "佰禾肥业",
+      "spec_type": "single"
+    },
+    {
+      "index": 5,
+      "id": "2039268890938216449",
+      "goods_id": "2039268890938216449",
+      "name": "谷润之藻生根",
+      "unit": "kg",
+      "price": "100",
+      "price_desc": "100元/kg",
+      "stock": 0,
+      "brand_name": "谷之润",
+      "spec_type": "single"
+    },
+    {
+      "index": 6,
+      "id": "2039268560259289090",
+      "goods_id": "2039268560259289090",
+      "name": "谷润之矿源腐植酸钾20-20-20",
+      "unit": "kg",
+      "price": "130",
+      "price_desc": "130元/kg",
+      "stock": 0,
+      "brand_name": "谷之润",
+      "spec_type": "single"
+    },
+    {
+      "index": 7,
+      "id": "2039268015851212802",
+      "goods_id": "2039268015851212802",
+      "name": "含腐植酸水溶肥",
+      "unit": "kg",
+      "price": "180",
+      "price_desc": "180元/kg",
+      "stock": 0,
+      "brand_name": "奥姆斯特",
+      "spec_type": "single"
+    },
+    {
+      "index": 8,
+      "id": "2039267600099217410",
+      "goods_id": "2039267600099217410",
+      "name": "百倍邦土壤调理剂",
+      "unit": "kg",
+      "price": "40",
+      "price_desc": "40元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 9,
+      "id": "2039267323740721154",
+      "goods_id": "2039267323740721154",
+      "name": "生物有机肥0.2亿（颗粒）",
+      "unit": "kg",
+      "price": "70",
+      "price_desc": "70元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 10,
+      "id": "2039266981347102721",
+      "goods_id": "2039266981347102721",
+      "name": "生物有机肥0.2亿（粉状）",
+      "unit": "kg",
+      "price": "60",
+      "price_desc": "60元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 11,
+      "id": "2039265582534135810",
+      "goods_id": "2039265582534135810",
+      "name": "洋丰豆生物有机肥",
+      "unit": "kg",
+      "price": "90",
+      "price_desc": "90元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 12,
+      "id": "2039265334109704193",
+      "goods_id": "2039265334109704193",
+      "name": "洋丰复合肥（追一道）玉米专用",
+      "unit": "kg",
+      "price": "125",
+      "price_desc": "125元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 13,
+      "id": "2039263960278011905",
+      "goods_id": "2039263960278011905",
+      "name": "洋丰锌磷镁复合肥25-10-16",
+      "unit": "kg",
+      "price": "180",
+      "price_desc": "180元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 14,
+      "id": "2039263622888198145",
+      "goods_id": "2039263622888198145",
+      "name": "洋丰锌磷镁复合肥17-17-17",
+      "unit": "kg",
+      "price": "220",
+      "price_desc": "220元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 15,
+      "id": "2039263225414979586",
+      "goods_id": "2039263225414979586",
+      "name": "洋丰复合肥14-16-15",
+      "unit": "kg",
+      "price": "160",
+      "price_desc": "160元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 16,
+      "id": "2039262979989475329",
+      "goods_id": "2039262979989475329",
+      "name": "洋丰复合肥15-15-15",
+      "unit": "kg",
+      "price": "160",
+      "price_desc": "160元/kg",
+      "stock": 0,
+      "brand_name": "新洋丰",
+      "spec_type": "single"
+    },
+    {
+      "index": 17,
+      "id": "2019743727796842497",
+      "goods_id": "2019743727796842497",
+      "name": "菌安天下",
+      "unit": "瓶",
+      "price": "19",
+      "price_desc": "19元/瓶",
+      "stock": 200,
+      "brand_name": "安利绿色",
+      "spec_type": "single"
+    }
+  ],
+  "category_cache_json": [],
+  "current_flow_id": "",
+  "goods_order_cache_json": [],
+  "last_goods_detail_json": {},
+  "next_shop_status": "WAITING_SELECT_GOODS",
+  "order_context_json": {
+    "goods_id": "",
+    "goods_name": "",
+    "sku_id": "",
+    "sku_name": "",
+    "quantity": "",
+    "address_id": "",
+    "address_text": ""
+  },
+  "reply_text": "我找到这些商品，您可以回复‘第几个商品’继续查看：\n1. 赤天化尿素（95元/袋，库存212）\n2. 西洋复合肥（15:15:15）（142.5元/袋，库存195）\n3. 赤天化复合肥（15:15:15）（142.5元/袋，库存200）\n4. 长效追一道（尿素）24:0:5（76元/袋，库存200）\n5. 谷润之藻生根（100元/kg，库存0）\n6. 谷润之矿源腐植酸钾20-20-20（130元/kg，库存0）\n7. 含腐植酸水溶肥（180元/kg，库存0）\n8. 百倍邦土壤调理剂（40元/kg，库存0）\n9. 生物有机肥0.2亿（颗粒）（70元/kg，库存0）\n10. 生物有机肥0.2亿（粉状）（60元/kg，库存0）"
+}
+[变量赋值 5]:
+{}
+[变量赋值 2]:
+{}
+[直接回复 2]:
+{
+  "answer": "我找到这些商品，您可以回复‘第几个商品’继续查看：\n1. 赤天化尿素（95元/袋，库存212）\n2. 西洋复合肥（15:15:15）（142.5元/袋，库存195）\n3. 赤天化复合肥（15:15:15）（142.5元/袋，库存200）\n4. 长效追一道（尿素）24:0:5（76元/袋，库存200）\n5. 谷润之藻生根（100元/kg，库存0）\n6. 谷润之矿源腐植酸钾20-20-20（130元/kg，库存0）\n7. 含腐植酸水溶肥（180元/kg，库存0）\n8. 百倍邦土壤调理剂（40元/kg，库存0）\n9. 生物有机肥0.2亿（颗粒）（70元/kg，库存0）\n10. 生物有机肥0.2亿（粉状）（60元/kg，库存0）",
+  "files": []
+}</t>
+  </si>
+  <si>
+    <t>11111</t>
+  </si>
+  <si>
+    <t>我要查一下上个月的订单</t>
+  </si>
+  <si>
+    <t>暂时没有查到相关订单，您可以换个订单号关键词再试试。</t>
+  </si>
+  <si>
+    <t>[用户输入]:
+{
+  "customer_id": "22222",
+  "sys.files": [],
+  "sys.user_id": "abc-123",
+  "sys.app_id": "735c9c90-b795-4287-b018-cc72f6a9106a",
+  "sys.workflow_id": "5675993e-1c2c-4071-98c1-699ff12b4516",
+  "sys.workflow_run_id": "0b37b5c0-f470-4e04-a6d2-a24dc145cf79",
+  "sys.query": "我要查一下上个月的订单",
+  "sys.conversation_id": "381617a3-1800-4b6d-b273-0be1f3747af4",
+  "sys.dialogue_count": 1
+}
+[路由判断]:
+{
+  "text": {
+    "intent": "SHOPPING",
+    "confidence": 96,
+    "switch_from": "",
+    "switch_to": "",
+    "clarify_question": "您是想查看上个月的所有订单，还是查询某个特定商品的订单呢？"
+  },
+  "reasoning_content": "",
+  "usage": {
+    "prompt_tokens": 401,
+    "prompt_unit_price": "0.86",
+    "prompt_price_unit": "0.000001",
+    "prompt_price": "0.0003449",
+    "completion_tokens": 44,
+    "completion_unit_price": "1.29",
+    "completion_price_unit": "0.000001",
+    "completion_price": "0.0000568",
+    "total_tokens": 445,
+    "total_price": "0.0004017",
+    "currency": "RMB",
+    "latency": 5.163,
+    "time_to_first_token": 2.951,
+    "time_to_generate": 2.212
+  },
+  "finish_reason": "stop"
+}
+[解析置信度JSON]:
+{
+  "clarify_question": "",
+  "clear_recommend": "clear",
+  "confidence": 96,
+  "confidence_level": "HIGH",
+  "intent_router": "SHOPPING",
+  "recommend_goods_id": "",
+  "recommend_goods_name": "",
+  "switch_from": "",
+  "switch_to": "",
+  "route_mode": "NORMAL"
+}
+[置信度≥95%？]:
+{
+  "result": true,
+  "selected_case_id": "true"
+}
+[切换预处理]:
+{
+  "dispatch_intent": "SHOPPING",
+  "dispatch_query": "我要查一下上个月的订单",
+  "shop_status": "IDLE",
+  "action": "",
+  "order_context": {},
+  "category_cache": [],
+  "candidate_cache": [],
+  "address_cache": [],
+  "last_goods_detail": {},
+  "current_flow_id": "",
+  "goods_order_cache": [],
+  "plot_status": "STAGE_SEARCH",
+  "contractor_cache": [],
+  "plot_cache": [],
+  "selected_contractor_code": "",
+  "selected_plot_id": "",
+  "selected_plot_name": "",
+  "fs_status": "STAGE_FS_SEARCH",
+  "fs_selected_service_id": "",
+  "fs_selected_service_name": "",
+  "fs_selected_unit_price": "",
+  "fs_selected_price_unit": "",
+  "fs_selected_plot_codes": "",
+  "fs_selected_plot_names": "",
+  "fs_selected_total_area": "",
+  "fs_expect_time": "",
+  "fs_remark": "",
+  "fs_candidate_cache": "",
+  "fs_plot_candidate_cache": "",
+  "fs_order_cache": "",
+  "pending_plot_indices": "",
+  "pending_time_text": "",
+  "in_recommend_flow": "false",
+  "recommend_candidate_cache": []
+}
+[写回切换状态]:
+{}
+[条件分支]:
+{
+  "result": true,
+  "selected_case_id": "true"
+}
+[下单LLM]:
+{
+  "text": {
+    "action": "search_goods_order",
+    "query": "上个月的订单"
+  },
+  "reasoning_content": "",
+  "usage": {
+    "prompt_tokens": 1037,
+    "prompt_unit_price": "0.86",
+    "prompt_price_unit": "0.000001",
+    "prompt_price": "0.0008918",
+    "completion_tokens": 15,
+    "completion_unit_price": "1.29",
+    "completion_price_unit": "0.000001",
+    "completion_price": "0.0000194",
+    "total_tokens": 1052,
+    "total_price": "0.0009112",
+    "currency": "RMB",
+    "latency": 5.549,
+    "time_to_first_token": 4.139,
+    "time_to_generate": 1.41
+  },
+  "finish_reason": "stop"
+}
+[变量提取]:
+{
+  "action": "search_goods_order",
+  "address_id": "",
+  "category_id": "",
+  "goods_id": "",
+  "order_id": "",
+  "quantity": "",
+  "query": "上个月的订单",
+  "sku_id": ""
+}
+[下单工具-v0.0.3-含订单查询]:
+{
+  "text": {
+    "reply_text": {
+      "action": "search_goods_order",
+      "reply_text": "暂时没有查到相关订单，您可以换个订单号关键词再试试。",
+      "shop_status": "IDLE",
+      "order_context": {},
+      "category_cache": [],
+      "candidate_cache": [],
+      "address_cache": [],
+      "last_goods_detail": {},
+      "current_flow_id": "",
+      "goods_order_cache": []
+    }
+  },
+  "files": [],
+  "json": [
+    {
+      "reply_text": {
+        "action": "search_goods_order",
+        "reply_text": "暂时没有查到相关订单，您可以换个订单号关键词再试试。",
+        "shop_status": "IDLE",
+        "order_context": {},
+        "category_cache": [],
+        "candidate_cache": [],
+        "address_cache": [],
+        "last_goods_detail": {},
+        "current_flow_id": "",
+        "goods_order_cache": []
+      }
+    }
+  ],
+  "reply_text": {
+    "action": "search_goods_order",
+    "reply_text": "暂时没有查到相关订单，您可以换个订单号关键词再试试。",
+    "shop_status": "IDLE",
+    "order_context": {},
+    "category_cache": [],
+    "candidate_cache": [],
+    "address_cache": [],
+    "last_goods_detail": {},
+    "current_flow_id": "",
+    "goods_order_cache": []
+  }
+}
+[代码执行 2]:
+{
+  "action": "search_goods_order",
+  "address_cache_json": [],
+  "candidate_cache_json": [],
+  "category_cache_json": [],
+  "current_flow_id": "",
+  "goods_order_cache_json": [],
+  "last_goods_detail_json": {},
+  "next_shop_status": "IDLE",
+  "order_context_json": {},
+  "reply_text": "暂时没有查到相关订单，您可以换个订单号关键词再试试。"
+}
+[变量赋值 5]:
+{}
+[变量赋值 2]:
+{}
+[直接回复 2]:
+{
+  "answer": "暂时没有查到相关订单，您可以换个订单号关键词再试试。",
+  "files": []
+}</t>
+  </si>
+  <si>
+    <t>22222</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -46,93 +1717,332 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -415,81 +2325,68 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>expect</t>
-        </is>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>gold_node_traces</t>
-        </is>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>买三包化肥</t>
-        </is>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>11111</t>
-        </is>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="409.5" spans="1:5">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>我要查一下上个月的订单</t>
-        </is>
+      <c r="B3" t="s">
+        <v>9</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>22222</t>
-        </is>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/data/chatflow_test_data.xlsx
+++ b/data/chatflow_test_data.xlsx
@@ -1,43 +1,931 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="100">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>expect</t>
+  </si>
+  <si>
+    <t>gold_node_traces</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>买两袋复合肥</t>
+  </si>
+  <si>
+    <t>SHOPPING</t>
+  </si>
+  <si>
+    <t>2011662594422755329</t>
+  </si>
+  <si>
+    <t>就选第1个吧</t>
+  </si>
+  <si>
+    <t>数量改成5包</t>
+  </si>
+  <si>
+    <t>送到列表里第2个地址</t>
+  </si>
+  <si>
+    <t>确认下单</t>
+  </si>
+  <si>
+    <t>看看肥料都有哪些分类</t>
+  </si>
+  <si>
+    <t>第一个分类</t>
+  </si>
+  <si>
+    <t>我要查一下刚才下的订单</t>
+  </si>
+  <si>
+    <t>查一下我名下的土地都在谁那</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>选第1个承包方</t>
+  </si>
+  <si>
+    <t>看看第2块地的详细信息</t>
+  </si>
+  <si>
+    <t>这块地看完了，返回上一级换个承包方看看</t>
+  </si>
+  <si>
+    <t>帮我统计一下我所有的地加起来总共有多少亩</t>
+  </si>
+  <si>
+    <t>我要找个无人机飞防打药</t>
+  </si>
+  <si>
+    <t>FARM_SERVICE</t>
+  </si>
+  <si>
+    <t>选第1个服务</t>
+  </si>
+  <si>
+    <t>在我的2号地打药</t>
+  </si>
+  <si>
+    <t>明天早上8点过来，备注一下大疆无人机</t>
+  </si>
+  <si>
+    <t>等等，服务选错了，重选服务</t>
+  </si>
+  <si>
+    <t>过两天玉米要收了，预约个收割机</t>
+  </si>
+  <si>
+    <t>第二个</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>买尿素</t>
+  </si>
+  <si>
+    <t>先不买了，查一下我的地</t>
+  </si>
+  <si>
+    <t>不查了，我要在这块地预约个旋耕</t>
+  </si>
+  <si>
+    <t>这块地我想改种大豆，现在的补贴政策是什么样的？</t>
+  </si>
+  <si>
+    <t>KNOWLEDGE</t>
+  </si>
+  <si>
+    <t>那给我买第1个除草剂</t>
+  </si>
+  <si>
+    <t>预约插秧</t>
+  </si>
+  <si>
+    <t>算了取消服务，我自己买点苗吧</t>
+  </si>
+  <si>
+    <t>买第2个</t>
+  </si>
+  <si>
+    <t>我要下单</t>
+  </si>
+  <si>
+    <t>买杀菌剂</t>
+  </si>
+  <si>
+    <t>哎呀点错了，重新开始吧</t>
+  </si>
+  <si>
+    <t>CHAT</t>
+  </si>
+  <si>
+    <t>我要查我名下的地</t>
+  </si>
+  <si>
+    <t>搜农药</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2个</t>
+    </r>
+  </si>
+  <si>
+    <t>不想买这个，重新选个商品</t>
+  </si>
+  <si>
+    <t>给我换第三个</t>
+  </si>
+  <si>
+    <t>买复合肥</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个，要3包</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3包</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等下，数量改成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5包</t>
+    </r>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>高级中学</t>
+  </si>
+  <si>
+    <t>下单</t>
+  </si>
+  <si>
+    <t>查我的订单</t>
+  </si>
+  <si>
+    <t>照上面的再下个单</t>
+  </si>
+  <si>
+    <t>我要找人打药</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个飞防服务</t>
+    </r>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>明天下午三点</t>
+  </si>
+  <si>
+    <t>确认</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>就在王家村玉米地，下周三下午来</t>
+  </si>
+  <si>
+    <t>算了，还要下雨，先不约了</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个服务</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>在我的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2号地打药</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>明天早上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点一刻过来，另外给我备注一下：大疆无人机，药水喷重点</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>等等，我选错地了，不是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2号地，换成3号地</t>
+    </r>
+  </si>
+  <si>
+    <t>查地</t>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个承包方</t>
+    </r>
+  </si>
+  <si>
+    <t>第一块地情况咋样</t>
+  </si>
+  <si>
+    <t>换个承包方看看</t>
+  </si>
+  <si>
+    <t>查地块</t>
+  </si>
+  <si>
+    <t>地块统计</t>
+  </si>
+  <si>
+    <t>帮我统计一下，我所有的地加起来总共有多少亩</t>
+  </si>
+  <si>
+    <t>那罗应兰名下有几块</t>
+  </si>
+  <si>
+    <t>除草剂应该什么时候打</t>
+  </si>
+  <si>
+    <r>
+      <t>那给我买第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个除草剂</t>
+    </r>
+  </si>
+  <si>
+    <t>帮我预约农机</t>
+  </si>
+  <si>
+    <r>
+      <t>选第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个承包方</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>选第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个</t>
+    </r>
+  </si>
+  <si>
+    <t>买点苗吧</t>
+  </si>
+  <si>
+    <t>买化肥</t>
+  </si>
+  <si>
+    <t>预约打药</t>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个</t>
+    </r>
+  </si>
+  <si>
+    <t>1号地</t>
+  </si>
+  <si>
+    <t>服务选错了，重选服务</t>
+  </si>
+  <si>
+    <t>预约飞防</t>
+  </si>
+  <si>
+    <t>我要在地里弄点东西</t>
+  </si>
+  <si>
+    <t>找农机服务</t>
+  </si>
+  <si>
+    <t>玉米叶子上长了虫子咋办</t>
+  </si>
+  <si>
+    <r>
+      <t>给我买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个除虫药</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF101828"/>
+        <rFont val="Segoe UI Emoji"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1个，来两瓶</t>
+    </r>
+  </si>
+  <si>
+    <t>人工插秧太慢了，有什么办法呢</t>
+  </si>
+  <si>
+    <t>搜一下种子</t>
+  </si>
+  <si>
+    <t>搜农药➔ 第2个➔ 不想买这个，重新选个商品</t>
+  </si>
+  <si>
+    <t>我要找人打药➔ 选第1个飞防服务➔ 1,2,3➔ 明天下午三点➔ 确认</t>
+  </si>
+  <si>
+    <t>查地➔ 第1个承包方➔第一块地情况咋样➔换个承包方看看➔ 第二个➔ 查地块</t>
+  </si>
+  <si>
+    <t>我要买点化肥➔ 就选第1个吧➔ 要10袋➔等等，我换个化肥看看➔我要买除草剂➔ 买第3个➔ 给我来20瓶</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF101828"/>
+      <name val="Segoe UI Emoji"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF101828"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -46,93 +934,345 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -415,81 +1555,1440 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="93.625" customWidth="1"/>
+    <col min="3" max="3" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="22.75" customWidth="1"/>
+    <col min="5" max="5" width="49.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>expect</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>gold_node_traces</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>买三包化肥</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>11111</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>我要查一下上个月的订单</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>22222</t>
-        </is>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:5">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:5">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:5">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:5">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:5">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:5">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:5">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:5">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:5">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:5">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:5">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:5">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:5">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:5">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:5">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:5">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:5">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:5">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:5">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:5">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:5">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:5">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:5">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:5">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:5">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:5">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:5">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:5">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:5">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:5">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:5">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:5">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:5">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:5">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" spans="1:5">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:5">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:5">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:5">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:5">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" t="s">
+        <v>34</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C75" t="s">
+        <v>34</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:5">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" t="s">
+        <v>6</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:5">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:5">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" t="s">
+        <v>6</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:5">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:5">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:5">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C81" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" spans="1:5">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" ht="16.5" spans="1:5">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83" t="s">
+        <v>6</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84" t="s">
+        <v>6</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" spans="1:5">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" t="s">
+        <v>6</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" spans="1:5">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C86" t="s">
+        <v>22</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" ht="16.5" spans="1:5">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C87" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" ht="16.5" spans="1:5">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C88" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" ht="16.5" spans="1:5">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C89" t="s">
+        <v>22</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" ht="16.5" spans="1:5">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90" t="s">
+        <v>22</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" ht="16.5" spans="1:5">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C91" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" ht="16.5" spans="1:5">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C92" t="s">
+        <v>22</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" ht="16.5" spans="1:5">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C93" t="s">
+        <v>34</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" ht="16.5" spans="1:5">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C94" t="s">
+        <v>6</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" ht="16.5" spans="1:5">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C95" t="s">
+        <v>6</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" ht="16.5" spans="1:5">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C96" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" ht="16.5" spans="1:5">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C97" t="s">
+        <v>6</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>96</v>
+      </c>
+      <c r="C98" t="s">
+        <v>6</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>97</v>
+      </c>
+      <c r="C99" t="s">
+        <v>22</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>98</v>
+      </c>
+      <c r="C100" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>99</v>
+      </c>
+      <c r="C101" t="s">
+        <v>6</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>